--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488132_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488132_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9087</v>
+        <v>5.1839</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1099</v>
+        <v>8.3605</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2012</v>
+        <v>-3.1766</v>
       </c>
       <c r="G2" t="n">
         <v>5.1969</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3542</v>
+        <v>-0.079</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4203</v>
+        <v>-0.1697</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.2512</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6135</v>
+        <v>0.9028</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3061</v>
+        <v>2.7185</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6926</v>
+        <v>-1.8157</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3652</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8108</v>
+        <v>0.1001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.725</v>
+        <v>0.1374</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0858</v>
+        <v>-0.0373</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5812</v>
+        <v>0.1703</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4445</v>
+        <v>3.1075</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8633</v>
+        <v>-2.9371</v>
       </c>
       <c r="G4" t="n">
         <v>0.1539</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6583</v>
+        <v>0.2475</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0074</v>
+        <v>-0.3444</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="V4" t="n">
         <v>0.8806</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3162</v>
+        <v>-0.9978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7388</v>
+        <v>1.0326</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.0551</v>
+        <v>-2.0304</v>
       </c>
       <c r="G5" t="n">
         <v>-0.9361</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.67</v>
+        <v>-0.3516</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5807</v>
+        <v>-0.2869</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0893</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-1.0071</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3373</v>
+        <v>-1.1409</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2218</v>
+        <v>0.3198</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5592</v>
+        <v>-1.4607</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2959</v>
@@ -922,13 +922,13 @@
         <v>0.3706</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1532</v>
+        <v>0.0432</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1641</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2589</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.397</v>
+        <v>-1.4895</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0422</v>
+        <v>-0.001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4392</v>
+        <v>-1.4885</v>
       </c>
       <c r="G7" t="n">
         <v>0.9678</v>
@@ -1000,13 +1000,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1736</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.051</v>
+        <v>0.0078</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1226</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>-0.315</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CARBU RODRIGUEZ</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1047</v>
+        <v>-1.6585</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7135</v>
+        <v>0.6622</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3912</v>
+        <v>-2.3206</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5659</v>
+        <v>-2.5002</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.755</v>
+        <v>1.4351</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-3.9353</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4611</v>
+        <v>-0.9728</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5026</v>
+        <v>0.8199</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>-1.7927</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1048</v>
+        <v>-1.5274</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2524</v>
+        <v>0.6152</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8524</v>
+        <v>-2.1426</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3315</v>
+        <v>0.3485</v>
       </c>
       <c r="T8" t="n">
-        <v>0.674</v>
+        <v>-0.2534</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3425</v>
+        <v>0.6019</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3144</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3144</v>
+        <v>-1.9509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>J. CARBU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1492</v>
+        <v>-2.3246</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3684</v>
+        <v>-1.0073</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5176</v>
+        <v>-1.3173</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5002</v>
+        <v>-1.5659</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4351</v>
+        <v>-0.755</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.9353</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9728</v>
+        <v>-0.4611</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8199</v>
+        <v>-0.5026</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.7927</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5274</v>
+        <v>-1.1048</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6152</v>
+        <v>-0.2524</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1426</v>
+        <v>-0.8524</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5558999999999999</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1423</v>
+        <v>0.1116</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5471</v>
+        <v>0.3802</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4049</v>
+        <v>-0.2686</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.3144</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9509</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4645</v>
+        <v>-4.4344</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3768</v>
+        <v>-0.3221</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0877</v>
+        <v>-4.1123</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3745</v>
@@ -1234,13 +1234,13 @@
         <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3542</v>
+        <v>0.3843</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0584</v>
+        <v>-0.0037</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4126</v>
+        <v>0.388</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2589</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9001</v>
+        <v>-6.5034</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1766</v>
+        <v>-4.6322</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7235</v>
+        <v>-1.8712</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5959</v>
@@ -1312,13 +1312,13 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.2329</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.3099</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2248</v>
+        <v>0.0771</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3777</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.5656</v>
+        <v>-12.2921</v>
       </c>
       <c r="E12" t="n">
-        <v>9.9648</v>
+        <v>10.2385</v>
       </c>
       <c r="F12" t="n">
-        <v>-22.5306</v>
+        <v>-22.5304</v>
       </c>
       <c r="G12" t="n">
         <v>-7.315100000000001</v>
@@ -1390,13 +1390,13 @@
         <v>10.1909</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3792</v>
+        <v>0.6527999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2371</v>
+        <v>-0.9635</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6165</v>
+        <v>1.6166</v>
       </c>
       <c r="V12" t="n">
         <v>-3.777299999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>D. LARA CALDERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7784</v>
+        <v>6.0686</v>
       </c>
       <c r="E13" t="n">
-        <v>7.9056</v>
+        <v>6.316</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1271</v>
+        <v>-0.2474</v>
       </c>
       <c r="G13" t="n">
-        <v>3.501</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6354</v>
+        <v>-4.6065</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1365</v>
+        <v>5.3358</v>
       </c>
       <c r="J13" t="n">
-        <v>5.7926</v>
+        <v>3.1483</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7177</v>
+        <v>-1.7573</v>
       </c>
       <c r="L13" t="n">
-        <v>4.0749</v>
+        <v>4.9055</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2915</v>
+        <v>-2.4189</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.3531</v>
+        <v>-2.8492</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0616</v>
+        <v>0.4303</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1117</v>
+        <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1657</v>
+        <v>0.2652</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5397</v>
+        <v>-0.3118</v>
       </c>
       <c r="U13" t="n">
-        <v>0.626</v>
+        <v>0.577</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.7771</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5733</v>
+        <v>4.406</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5733</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LARA CALDERA</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7674</v>
+        <v>5.1898</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0222</v>
+        <v>7.5139</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2549</v>
+        <v>-2.3241</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7292999999999999</v>
+        <v>3.501</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.6065</v>
+        <v>-0.6354</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3358</v>
+        <v>4.1365</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1483</v>
+        <v>5.7926</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.7573</v>
+        <v>1.7177</v>
       </c>
       <c r="L14" t="n">
-        <v>4.9055</v>
+        <v>4.0749</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4189</v>
+        <v>-2.2915</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.8492</v>
+        <v>-2.3531</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4303</v>
+        <v>0.0616</v>
       </c>
       <c r="P14" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2234</v>
+        <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0361</v>
+        <v>0.577</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6056</v>
+        <v>0.148</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5695</v>
+        <v>0.429</v>
       </c>
       <c r="V14" t="n">
-        <v>3.7771</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.406</v>
+        <v>1.5733</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6289</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.764</v>
+        <v>4.3294</v>
       </c>
       <c r="E15" t="n">
-        <v>6.8765</v>
+        <v>6.6806</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1124</v>
+        <v>-2.3512</v>
       </c>
       <c r="G15" t="n">
         <v>1.6328</v>
@@ -1624,13 +1624,13 @@
         <v>2.2234</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8904</v>
+        <v>0.4558</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2114</v>
+        <v>0.0156</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.4402</v>
       </c>
       <c r="V15" t="n">
         <v>0.9439</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.104</v>
+        <v>3.4612</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9456</v>
+        <v>2.7291</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1584</v>
+        <v>0.7321</v>
       </c>
       <c r="G16" t="n">
         <v>3.118</v>
@@ -1702,13 +1702,13 @@
         <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3846</v>
+        <v>-0.0274</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0943</v>
+        <v>-0.3109</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2903</v>
+        <v>0.2835</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.545</v>
       </c>
       <c r="E20" t="n">
         <v>0.4303</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0246</v>
+        <v>-0.9754</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0391</v>
@@ -2014,13 +2014,13 @@
         <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.426</v>
+        <v>-0.3768</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3283</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2792</v>
+        <v>-1.2964</v>
       </c>
       <c r="E21" t="n">
         <v>-1.3289</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0497</v>
+        <v>0.0325</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1706</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1328</v>
+        <v>0.1156</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2773</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4101</v>
+        <v>0.3929</v>
       </c>
       <c r="V21" t="n">
         <v>-0.315</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5115</v>
+        <v>-1.413</v>
       </c>
       <c r="E22" t="n">
         <v>-0.91</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6015</v>
+        <v>-0.503</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4107</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1743</v>
+        <v>-0.0759</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0649</v>
+        <v>0.0336</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4172</v>
+        <v>-2.4562</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3717</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0454</v>
+        <v>-1.5948</v>
       </c>
       <c r="G23" t="n">
         <v>-2.106</v>
@@ -2248,13 +2248,13 @@
         <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0032</v>
+        <v>-0.0358</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4303</v>
+        <v>-0.0594</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.427</v>
+        <v>0.0236</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3144</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5564</v>
+        <v>-2.6302</v>
       </c>
       <c r="E24" t="n">
         <v>-0.5494</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0069</v>
+        <v>-2.0808</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4501</v>
@@ -2326,13 +2326,13 @@
         <v>0.3706</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5504</v>
+        <v>-0.6243</v>
       </c>
       <c r="T24" t="n">
         <v>-0.383</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1674</v>
+        <v>-0.2413</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>12.5656</v>
+        <v>13.2186</v>
       </c>
       <c r="E25" t="n">
         <v>22.5306</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.964700000000001</v>
+        <v>-9.312100000000001</v>
       </c>
       <c r="G25" t="n">
         <v>7.315</v>
@@ -2404,13 +2404,13 @@
         <v>12.0436</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3793000000000002</v>
+        <v>0.2734</v>
       </c>
       <c r="T25" t="n">
         <v>-1.6165</v>
       </c>
       <c r="U25" t="n">
-        <v>1.2372</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
         <v>3.7772</v>
